--- a/WebDataAgro/Templates/AltaMasivaSugerenciaDeCupos.xlsx
+++ b/WebDataAgro/Templates/AltaMasivaSugerenciaDeCupos.xlsx
@@ -35,9 +35,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -105,25 +104,9 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="1">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -315,279 +298,27 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C85"/>
-  <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="14.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="14.74"/>
-  </cols>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="0" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="0" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0"/>
-      <c r="B2" s="0"/>
-      <c r="C2" s="0"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="2"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="2"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="2"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="2"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="2"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="2"/>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="2"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="2"/>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="2"/>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="2"/>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="2"/>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="2"/>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="2"/>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="2"/>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="2"/>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="2"/>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="2"/>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="2"/>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="2"/>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="2"/>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="2"/>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="2"/>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="2"/>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="2"/>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="2"/>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="2"/>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="2"/>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="2"/>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="2"/>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="2"/>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="2"/>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="2"/>
-    </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="2"/>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="2"/>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="2"/>
-    </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="2"/>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="2"/>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="2"/>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="2"/>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="2"/>
-    </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="2"/>
-    </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="2"/>
-    </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="2"/>
-    </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="2"/>
-    </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="2"/>
-    </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="2"/>
-    </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="2"/>
-    </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="2"/>
-    </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="2"/>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="2"/>
-    </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="2"/>
-    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
